--- a/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>08:36</v>
+        <v>21:10</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>אייל גולן - 30 חלק ג</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24463&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:10</v>
+        <v>21:11</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ג</v>
+        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-04-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24464&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=21671&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21:11</v>
+        <v>11:50</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מחווה לשירי יאיר רוזנבלום בכאן גימל - המנגינה היא שקובעת</v>
+        <v>אוסף ענק: וזוהי רק ההתחלה - 300 השירים הגדולים של הלהקות הצבאיות</v>
       </c>
     </row>
   </sheetData>
